--- a/Usability_testing.xlsx
+++ b/Usability_testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Vibhuti\Software Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697776AC-1245-41F8-818F-DA0BE5FADD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4FB8BC-8EF2-4082-8DD2-2387432C44CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{7767BF9E-3B7E-4D24-981A-65D0966D29C7}"/>
   </bookViews>
